--- a/cards/04-opisatelnaya-statistika.xlsx
+++ b/cards/04-opisatelnaya-statistika.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/meikinai/Desktop/flashcards-site/cards/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B5FAA33-9AB1-BA4B-8864-9066D37CE397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A87636-67F7-4A40-A2DD-56806739960D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Карточки" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Карточки!$A$1:$I$56</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="150">
   <si>
     <t>Модуль</t>
   </si>
@@ -449,6 +448,45 @@
   </si>
   <si>
     <t>Модуль 1: Анализ и визуализация данных в Excel</t>
+  </si>
+  <si>
+    <t>=AVERAGE(диапазон)</t>
+  </si>
+  <si>
+    <t>=AVERAGE(B2:B22)</t>
+  </si>
+  <si>
+    <t>=MEDIAN(диапазон)</t>
+  </si>
+  <si>
+    <t>=MEDIAN(B2:B22)</t>
+  </si>
+  <si>
+    <t>=@MODE.SNGL(диапазон)</t>
+  </si>
+  <si>
+    <t>=@MODE.SNGL(B2:B22)</t>
+  </si>
+  <si>
+    <t>=MAX(диапазон)-MIN(диапазон)</t>
+  </si>
+  <si>
+    <t>=MAX(B2:B22)-MIN(B2:B22)</t>
+  </si>
+  <si>
+    <t>=@VAR.S(диапазон)</t>
+  </si>
+  <si>
+    <t>=@VAR.S(B2:B22)</t>
+  </si>
+  <si>
+    <t>=@STDEV.S(диапазон)</t>
+  </si>
+  <si>
+    <t>=@STDEV.S(B2:B22)</t>
+  </si>
+  <si>
+    <t>=SQRT(@число)</t>
   </si>
 </sst>
 </file>
@@ -522,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -538,6 +576,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -851,7 +895,7 @@
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="70" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="37.1640625" customWidth="1"/>
+    <col min="7" max="7" width="37.1640625" style="4" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="50" customWidth="1"/>
   </cols>
@@ -875,7 +919,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -908,7 +952,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>136</v>
       </c>
@@ -931,7 +975,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>136</v>
       </c>
@@ -954,7 +998,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>136</v>
       </c>
@@ -973,17 +1017,15 @@
       <c r="F5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="2" t="e">
-        <f>AVERAGE(диапазон)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="H5" s="2" t="e">
-        <f>AVERAGE(B2:B22)</f>
-        <v>#DIV/0!</v>
+      <c r="G5" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>136</v>
       </c>
@@ -1006,7 +1048,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>136</v>
       </c>
@@ -1029,7 +1071,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>136</v>
       </c>
@@ -1048,17 +1090,15 @@
       <c r="F8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="2" t="e">
-        <f>MEDIAN(диапазон)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="H8" s="2" t="e">
-        <f>MEDIAN(B2:B22)</f>
-        <v>#NUM!</v>
+      <c r="G8" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>136</v>
       </c>
@@ -1081,7 +1121,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>136</v>
       </c>
@@ -1100,14 +1140,13 @@
       <c r="F10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="2" t="e">
-        <f>MEDIAN(диапазон)</f>
-        <v>#NAME?</v>
+      <c r="G10" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>136</v>
       </c>
@@ -1130,7 +1169,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>136</v>
       </c>
@@ -1149,17 +1188,15 @@
       <c r="F12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="2" t="e">
-        <f ca="1">_xludf.MODE.SNGL(диапазон)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="H12" s="2" t="e">
-        <f ca="1">_xludf.MODE.SNGL(B2:B22)</f>
-        <v>#NAME?</v>
+      <c r="G12" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>136</v>
       </c>
@@ -1182,7 +1219,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>136</v>
       </c>
@@ -1205,7 +1242,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>136</v>
       </c>
@@ -1228,7 +1265,7 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>136</v>
       </c>
@@ -1251,7 +1288,7 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>136</v>
       </c>
@@ -1274,7 +1311,7 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>136</v>
       </c>
@@ -1297,7 +1334,7 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>136</v>
       </c>
@@ -1320,7 +1357,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>136</v>
       </c>
@@ -1343,7 +1380,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>136</v>
       </c>
@@ -1366,7 +1403,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>136</v>
       </c>
@@ -1389,7 +1426,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>136</v>
       </c>
@@ -1412,7 +1449,7 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>136</v>
       </c>
@@ -1435,7 +1472,7 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>136</v>
       </c>
@@ -1458,7 +1495,7 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>136</v>
       </c>
@@ -1481,7 +1518,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>136</v>
       </c>
@@ -1504,7 +1541,7 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>136</v>
       </c>
@@ -1527,7 +1564,7 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>136</v>
       </c>
@@ -1550,7 +1587,7 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>136</v>
       </c>
@@ -1573,7 +1610,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>136</v>
       </c>
@@ -1596,7 +1633,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>136</v>
       </c>
@@ -1619,7 +1656,7 @@
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>136</v>
       </c>
@@ -1638,17 +1675,15 @@
       <c r="F33" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G33" s="2" t="e">
-        <f>MAX(диапазон)-MIN(диапазон)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="H33" s="2">
-        <f>MAX(B2:B22)-MIN(B2:B22)</f>
-        <v>0</v>
+      <c r="G33" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>136</v>
       </c>
@@ -1671,7 +1706,7 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>136</v>
       </c>
@@ -1694,7 +1729,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>136</v>
       </c>
@@ -1713,17 +1748,15 @@
       <c r="F36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G36" s="2" t="e">
-        <f ca="1">_xludf.VAR.S(диапазон)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="H36" s="2" t="e">
-        <f ca="1">_xludf.VAR.S(B2:B22)</f>
-        <v>#NAME?</v>
+      <c r="G36" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>136</v>
       </c>
@@ -1742,14 +1775,13 @@
       <c r="F37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G37" s="2" t="e">
-        <f ca="1">_xludf.VAR.S(диапазон)</f>
-        <v>#NAME?</v>
+      <c r="G37" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>136</v>
       </c>
@@ -1772,7 +1804,7 @@
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>136</v>
       </c>
@@ -1795,7 +1827,7 @@
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>136</v>
       </c>
@@ -1818,7 +1850,7 @@
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>136</v>
       </c>
@@ -1837,17 +1869,15 @@
       <c r="F41" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G41" s="2" t="e">
-        <f ca="1">_xludf.STDEV.S(диапазон)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="H41" s="2" t="e">
-        <f ca="1">_xludf.STDEV.S(B2:B22)</f>
-        <v>#NAME?</v>
+      <c r="G41" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>136</v>
       </c>
@@ -1870,7 +1900,7 @@
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>136</v>
       </c>
@@ -1893,7 +1923,7 @@
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>136</v>
       </c>
@@ -1912,14 +1942,13 @@
       <c r="F44" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G44" s="2" t="e">
-        <f>SQRT(число)</f>
-        <v>#NAME?</v>
+      <c r="G44" s="8" t="s">
+        <v>149</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>136</v>
       </c>
@@ -1942,7 +1971,7 @@
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>136</v>
       </c>
@@ -1965,7 +1994,7 @@
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>136</v>
       </c>
@@ -1988,7 +2017,7 @@
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
     </row>
-    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>136</v>
       </c>
@@ -2011,7 +2040,7 @@
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
     </row>
-    <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>136</v>
       </c>
@@ -2034,7 +2063,7 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>136</v>
       </c>
@@ -2057,7 +2086,7 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>136</v>
       </c>
@@ -2080,7 +2109,7 @@
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>136</v>
       </c>
@@ -2103,7 +2132,7 @@
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
     </row>
-    <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>136</v>
       </c>
@@ -2126,7 +2155,7 @@
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
     </row>
-    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>136</v>
       </c>
@@ -2149,7 +2178,7 @@
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>136</v>
       </c>
@@ -2172,7 +2201,7 @@
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>136</v>
       </c>
@@ -2301,7 +2330,6 @@
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
     </row>
@@ -2312,7 +2340,6 @@
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
     </row>
@@ -2323,7 +2350,6 @@
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
     </row>
@@ -2334,7 +2360,6 @@
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
     </row>
@@ -2345,7 +2370,6 @@
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
     </row>
@@ -2356,7 +2380,6 @@
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
     </row>
@@ -2367,7 +2390,6 @@
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
     </row>
@@ -2378,7 +2400,6 @@
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
     </row>
@@ -2389,7 +2410,6 @@
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
     </row>
@@ -2400,7 +2420,6 @@
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
     </row>
@@ -2411,7 +2430,6 @@
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
     </row>
@@ -2422,7 +2440,6 @@
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
     </row>
@@ -2433,7 +2450,6 @@
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
     </row>
@@ -2444,7 +2460,6 @@
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
     </row>
@@ -2455,7 +2470,6 @@
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
-      <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
     </row>
@@ -2466,7 +2480,6 @@
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
-      <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
     </row>
@@ -2477,7 +2490,6 @@
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
     </row>
@@ -2488,7 +2500,6 @@
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
-      <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
     </row>
@@ -2499,7 +2510,6 @@
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
-      <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
     </row>
@@ -2510,7 +2520,6 @@
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
     </row>
@@ -2521,7 +2530,6 @@
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
     </row>
@@ -2532,7 +2540,6 @@
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
     </row>
@@ -2543,7 +2550,6 @@
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
     </row>
@@ -2554,7 +2560,6 @@
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
     </row>
@@ -2565,7 +2570,6 @@
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
     </row>
@@ -2576,7 +2580,6 @@
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
     </row>
@@ -2587,7 +2590,6 @@
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
     </row>
@@ -2598,7 +2600,6 @@
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
     </row>
@@ -2609,7 +2610,6 @@
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
     </row>
@@ -2620,7 +2620,6 @@
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
     </row>
@@ -2631,7 +2630,6 @@
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
     </row>
@@ -2642,7 +2640,6 @@
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
     </row>
@@ -2653,7 +2650,6 @@
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
     </row>
@@ -2664,7 +2660,6 @@
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
     </row>
@@ -2675,7 +2670,6 @@
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
       <c r="H100" s="4"/>
       <c r="I100" s="4"/>
     </row>
@@ -2686,7 +2680,6 @@
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
     </row>
@@ -2697,7 +2690,6 @@
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
     </row>
@@ -2708,7 +2700,6 @@
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
     </row>
@@ -2719,7 +2710,6 @@
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
     </row>
@@ -2730,7 +2720,6 @@
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
     </row>
@@ -2741,7 +2730,6 @@
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
     </row>
@@ -2752,7 +2740,6 @@
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
     </row>
@@ -2763,7 +2750,6 @@
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
     </row>
@@ -2774,7 +2760,6 @@
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
     </row>
@@ -2785,7 +2770,6 @@
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
     </row>
@@ -2796,7 +2780,6 @@
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
     </row>
@@ -2807,7 +2790,6 @@
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
     </row>
@@ -2818,7 +2800,6 @@
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
     </row>
@@ -2829,7 +2810,6 @@
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
-      <c r="G114" s="4"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
     </row>
@@ -2840,7 +2820,6 @@
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
-      <c r="G115" s="4"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
     </row>
@@ -2851,7 +2830,6 @@
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
     </row>
@@ -2862,7 +2840,6 @@
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
     </row>
@@ -2873,7 +2850,6 @@
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
-      <c r="G118" s="4"/>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
     </row>
@@ -2884,7 +2860,6 @@
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
-      <c r="G119" s="4"/>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
     </row>
@@ -2895,7 +2870,6 @@
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
-      <c r="G120" s="4"/>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
     </row>
@@ -2906,7 +2880,6 @@
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
-      <c r="G121" s="4"/>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
     </row>
@@ -2917,7 +2890,6 @@
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
     </row>
@@ -2928,7 +2900,6 @@
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
-      <c r="G123" s="4"/>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
     </row>
@@ -2939,7 +2910,6 @@
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
-      <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
     </row>
@@ -2950,7 +2920,6 @@
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
     </row>
@@ -2961,7 +2930,6 @@
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
-      <c r="G126" s="4"/>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
     </row>
@@ -2972,7 +2940,6 @@
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
-      <c r="G127" s="4"/>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
     </row>
@@ -2983,7 +2950,6 @@
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
     </row>
@@ -2994,7 +2960,6 @@
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
-      <c r="G129" s="4"/>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
     </row>
@@ -3005,7 +2970,6 @@
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
     </row>
@@ -3016,7 +2980,6 @@
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
-      <c r="G131" s="4"/>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
     </row>
@@ -3027,7 +2990,6 @@
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
-      <c r="G132" s="4"/>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
     </row>
@@ -3038,7 +3000,6 @@
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
     </row>
@@ -3049,7 +3010,6 @@
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
-      <c r="G134" s="4"/>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
     </row>
@@ -3060,7 +3020,6 @@
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
-      <c r="G135" s="4"/>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
     </row>
@@ -3071,7 +3030,6 @@
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
     </row>
@@ -3082,7 +3040,6 @@
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
     </row>
@@ -3093,7 +3050,6 @@
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
     </row>
@@ -3104,7 +3060,6 @@
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
-      <c r="G139" s="4"/>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
     </row>
@@ -3115,7 +3070,6 @@
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
-      <c r="G140" s="4"/>
       <c r="H140" s="4"/>
       <c r="I140" s="4"/>
     </row>
@@ -3126,7 +3080,6 @@
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
       <c r="H141" s="4"/>
       <c r="I141" s="4"/>
     </row>
@@ -3137,7 +3090,6 @@
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
-      <c r="G142" s="4"/>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
     </row>
@@ -3148,7 +3100,6 @@
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
-      <c r="G143" s="4"/>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
     </row>
@@ -3159,7 +3110,6 @@
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
     </row>
@@ -3170,7 +3120,6 @@
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
-      <c r="G145" s="4"/>
       <c r="H145" s="4"/>
       <c r="I145" s="4"/>
     </row>
@@ -3181,7 +3130,6 @@
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
-      <c r="G146" s="4"/>
       <c r="H146" s="4"/>
       <c r="I146" s="4"/>
     </row>
@@ -3192,7 +3140,6 @@
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
-      <c r="G147" s="4"/>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
     </row>
@@ -3203,7 +3150,6 @@
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
-      <c r="G148" s="4"/>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
     </row>
@@ -3214,7 +3160,6 @@
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
-      <c r="G149" s="4"/>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
     </row>
@@ -3225,7 +3170,6 @@
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
-      <c r="G150" s="4"/>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
     </row>
@@ -3236,7 +3180,6 @@
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
-      <c r="G151" s="4"/>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
     </row>
@@ -3247,7 +3190,6 @@
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
     </row>
@@ -3258,7 +3200,6 @@
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
-      <c r="G153" s="4"/>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
     </row>
@@ -3269,7 +3210,6 @@
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
-      <c r="G154" s="4"/>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
     </row>
@@ -3280,7 +3220,6 @@
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
-      <c r="G155" s="4"/>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
     </row>
@@ -3291,7 +3230,6 @@
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
-      <c r="G156" s="4"/>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
     </row>
@@ -3302,7 +3240,6 @@
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
-      <c r="G157" s="4"/>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
     </row>
@@ -3313,7 +3250,6 @@
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
-      <c r="G158" s="4"/>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
     </row>
@@ -3324,7 +3260,6 @@
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
-      <c r="G159" s="4"/>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
     </row>
@@ -3335,7 +3270,6 @@
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
-      <c r="G160" s="4"/>
       <c r="H160" s="4"/>
       <c r="I160" s="4"/>
     </row>
@@ -3346,7 +3280,6 @@
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
-      <c r="G161" s="4"/>
       <c r="H161" s="4"/>
       <c r="I161" s="4"/>
     </row>
@@ -3357,7 +3290,6 @@
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
-      <c r="G162" s="4"/>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
     </row>
@@ -3368,7 +3300,6 @@
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
-      <c r="G163" s="4"/>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
     </row>
@@ -3379,7 +3310,6 @@
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
-      <c r="G164" s="4"/>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
     </row>
@@ -3390,7 +3320,6 @@
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
-      <c r="G165" s="4"/>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
     </row>
@@ -3401,7 +3330,6 @@
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
-      <c r="G166" s="4"/>
       <c r="H166" s="4"/>
       <c r="I166" s="4"/>
     </row>
@@ -3412,7 +3340,6 @@
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
-      <c r="G167" s="4"/>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
     </row>
@@ -3423,7 +3350,6 @@
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
-      <c r="G168" s="4"/>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
     </row>
@@ -3434,7 +3360,6 @@
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
-      <c r="G169" s="4"/>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
     </row>
@@ -3445,7 +3370,6 @@
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
       <c r="F170" s="4"/>
-      <c r="G170" s="4"/>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
     </row>
@@ -3456,7 +3380,6 @@
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
-      <c r="G171" s="4"/>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
     </row>
@@ -3467,7 +3390,6 @@
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
-      <c r="G172" s="4"/>
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
     </row>
@@ -3478,7 +3400,6 @@
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
-      <c r="G173" s="4"/>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
     </row>
@@ -3489,7 +3410,6 @@
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
-      <c r="G174" s="4"/>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
     </row>
@@ -3500,7 +3420,6 @@
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
-      <c r="G175" s="4"/>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
     </row>
@@ -3511,7 +3430,6 @@
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
-      <c r="G176" s="4"/>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
     </row>
@@ -3522,7 +3440,6 @@
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
-      <c r="G177" s="4"/>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
     </row>
@@ -3533,7 +3450,6 @@
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
-      <c r="G178" s="4"/>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
     </row>
@@ -3544,7 +3460,6 @@
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
       <c r="F179" s="4"/>
-      <c r="G179" s="4"/>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
     </row>
@@ -3555,7 +3470,6 @@
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
-      <c r="G180" s="4"/>
       <c r="H180" s="4"/>
       <c r="I180" s="4"/>
     </row>
@@ -3566,7 +3480,6 @@
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
-      <c r="G181" s="4"/>
       <c r="H181" s="4"/>
       <c r="I181" s="4"/>
     </row>
@@ -3577,7 +3490,6 @@
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
-      <c r="G182" s="4"/>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
     </row>
@@ -3588,7 +3500,6 @@
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
-      <c r="G183" s="4"/>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
     </row>
@@ -3599,7 +3510,6 @@
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
-      <c r="G184" s="4"/>
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
     </row>
@@ -3610,7 +3520,6 @@
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
-      <c r="G185" s="4"/>
       <c r="H185" s="4"/>
       <c r="I185" s="4"/>
     </row>
@@ -3621,7 +3530,6 @@
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
       <c r="F186" s="4"/>
-      <c r="G186" s="4"/>
       <c r="H186" s="4"/>
       <c r="I186" s="4"/>
     </row>
@@ -3632,7 +3540,6 @@
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
       <c r="F187" s="4"/>
-      <c r="G187" s="4"/>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
     </row>
@@ -3643,7 +3550,6 @@
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
       <c r="F188" s="4"/>
-      <c r="G188" s="4"/>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
     </row>
@@ -3654,7 +3560,6 @@
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
-      <c r="G189" s="4"/>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
     </row>
@@ -3665,7 +3570,6 @@
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
       <c r="F190" s="4"/>
-      <c r="G190" s="4"/>
       <c r="H190" s="4"/>
       <c r="I190" s="4"/>
     </row>
@@ -3676,7 +3580,6 @@
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
-      <c r="G191" s="4"/>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
     </row>
@@ -3687,7 +3590,6 @@
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
-      <c r="G192" s="4"/>
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
     </row>
@@ -3698,7 +3600,6 @@
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
-      <c r="G193" s="4"/>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
     </row>
@@ -3709,7 +3610,6 @@
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
-      <c r="G194" s="4"/>
       <c r="H194" s="4"/>
       <c r="I194" s="4"/>
     </row>
@@ -3720,7 +3620,6 @@
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
     </row>
@@ -3731,7 +3630,6 @@
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
-      <c r="G196" s="4"/>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
     </row>
@@ -3742,7 +3640,6 @@
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
-      <c r="G197" s="4"/>
       <c r="H197" s="4"/>
       <c r="I197" s="4"/>
     </row>
@@ -3753,7 +3650,6 @@
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
       <c r="F198" s="4"/>
-      <c r="G198" s="4"/>
       <c r="H198" s="4"/>
       <c r="I198" s="4"/>
     </row>
@@ -3764,7 +3660,6 @@
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
-      <c r="G199" s="4"/>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
     </row>
@@ -3775,7 +3670,6 @@
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
       <c r="F200" s="4"/>
-      <c r="G200" s="4"/>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
     </row>
@@ -3786,7 +3680,6 @@
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
-      <c r="G201" s="4"/>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
     </row>
@@ -3797,7 +3690,6 @@
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
       <c r="F202" s="4"/>
-      <c r="G202" s="4"/>
       <c r="H202" s="4"/>
       <c r="I202" s="4"/>
     </row>
@@ -3808,7 +3700,6 @@
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
       <c r="F203" s="4"/>
-      <c r="G203" s="4"/>
       <c r="H203" s="4"/>
       <c r="I203" s="4"/>
     </row>
@@ -3819,7 +3710,6 @@
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
       <c r="F204" s="4"/>
-      <c r="G204" s="4"/>
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
     </row>
@@ -3830,7 +3720,6 @@
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
       <c r="F205" s="4"/>
-      <c r="G205" s="4"/>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
     </row>
@@ -3841,7 +3730,6 @@
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
       <c r="F206" s="4"/>
-      <c r="G206" s="4"/>
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
     </row>
@@ -3852,7 +3740,6 @@
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
       <c r="F207" s="4"/>
-      <c r="G207" s="4"/>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
     </row>
@@ -3863,7 +3750,6 @@
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
       <c r="F208" s="4"/>
-      <c r="G208" s="4"/>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
     </row>
@@ -3874,7 +3760,6 @@
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
       <c r="F209" s="4"/>
-      <c r="G209" s="4"/>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
     </row>
@@ -3885,7 +3770,6 @@
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
-      <c r="G210" s="4"/>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
     </row>
@@ -3896,7 +3780,6 @@
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
-      <c r="G211" s="4"/>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
     </row>
@@ -3907,7 +3790,6 @@
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
-      <c r="G212" s="4"/>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
     </row>
@@ -3918,7 +3800,6 @@
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
-      <c r="G213" s="4"/>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
     </row>
@@ -3929,7 +3810,6 @@
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
-      <c r="G214" s="4"/>
       <c r="H214" s="4"/>
       <c r="I214" s="4"/>
     </row>
@@ -3940,7 +3820,6 @@
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
-      <c r="G215" s="4"/>
       <c r="H215" s="4"/>
       <c r="I215" s="4"/>
     </row>
@@ -3951,7 +3830,6 @@
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
-      <c r="G216" s="4"/>
       <c r="H216" s="4"/>
       <c r="I216" s="4"/>
     </row>
@@ -3962,7 +3840,6 @@
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
-      <c r="G217" s="4"/>
       <c r="H217" s="4"/>
       <c r="I217" s="4"/>
     </row>
@@ -3973,7 +3850,6 @@
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
-      <c r="G218" s="4"/>
       <c r="H218" s="4"/>
       <c r="I218" s="4"/>
     </row>
@@ -3984,7 +3860,6 @@
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
-      <c r="G219" s="4"/>
       <c r="H219" s="4"/>
       <c r="I219" s="4"/>
     </row>
@@ -3995,7 +3870,6 @@
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
-      <c r="G220" s="4"/>
       <c r="H220" s="4"/>
       <c r="I220" s="4"/>
     </row>
@@ -4006,7 +3880,6 @@
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
-      <c r="G221" s="4"/>
       <c r="H221" s="4"/>
       <c r="I221" s="4"/>
     </row>
@@ -4017,7 +3890,6 @@
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
-      <c r="G222" s="4"/>
       <c r="H222" s="4"/>
       <c r="I222" s="4"/>
     </row>
@@ -4028,7 +3900,6 @@
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
-      <c r="G223" s="4"/>
       <c r="H223" s="4"/>
       <c r="I223" s="4"/>
     </row>
@@ -4039,7 +3910,6 @@
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
-      <c r="G224" s="4"/>
       <c r="H224" s="4"/>
       <c r="I224" s="4"/>
     </row>
@@ -4050,7 +3920,6 @@
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
-      <c r="G225" s="4"/>
       <c r="H225" s="4"/>
       <c r="I225" s="4"/>
     </row>
@@ -4061,7 +3930,6 @@
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
       <c r="F226" s="4"/>
-      <c r="G226" s="4"/>
       <c r="H226" s="4"/>
       <c r="I226" s="4"/>
     </row>
@@ -4072,7 +3940,6 @@
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
       <c r="F227" s="4"/>
-      <c r="G227" s="4"/>
       <c r="H227" s="4"/>
       <c r="I227" s="4"/>
     </row>
@@ -4083,7 +3950,6 @@
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
-      <c r="G228" s="4"/>
       <c r="H228" s="4"/>
       <c r="I228" s="4"/>
     </row>
@@ -4094,7 +3960,6 @@
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
       <c r="F229" s="4"/>
-      <c r="G229" s="4"/>
       <c r="H229" s="4"/>
       <c r="I229" s="4"/>
     </row>
@@ -4105,7 +3970,6 @@
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="4"/>
-      <c r="G230" s="4"/>
       <c r="H230" s="4"/>
       <c r="I230" s="4"/>
     </row>
@@ -4116,7 +3980,6 @@
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
-      <c r="G231" s="4"/>
       <c r="H231" s="4"/>
       <c r="I231" s="4"/>
     </row>
@@ -4127,7 +3990,6 @@
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
       <c r="F232" s="4"/>
-      <c r="G232" s="4"/>
       <c r="H232" s="4"/>
       <c r="I232" s="4"/>
     </row>
@@ -4138,7 +4000,6 @@
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="4"/>
-      <c r="G233" s="4"/>
       <c r="H233" s="4"/>
       <c r="I233" s="4"/>
     </row>
@@ -4149,7 +4010,6 @@
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
       <c r="H234" s="4"/>
       <c r="I234" s="4"/>
     </row>
@@ -4160,7 +4020,6 @@
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
-      <c r="G235" s="4"/>
       <c r="H235" s="4"/>
       <c r="I235" s="4"/>
     </row>
@@ -4171,7 +4030,6 @@
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
-      <c r="G236" s="4"/>
       <c r="H236" s="4"/>
       <c r="I236" s="4"/>
     </row>
@@ -4182,7 +4040,6 @@
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
-      <c r="G237" s="4"/>
       <c r="H237" s="4"/>
       <c r="I237" s="4"/>
     </row>
@@ -4193,7 +4050,6 @@
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
-      <c r="G238" s="4"/>
       <c r="H238" s="4"/>
       <c r="I238" s="4"/>
     </row>
@@ -4204,7 +4060,6 @@
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
-      <c r="G239" s="4"/>
       <c r="H239" s="4"/>
       <c r="I239" s="4"/>
     </row>
@@ -4215,7 +4070,6 @@
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
       <c r="F240" s="4"/>
-      <c r="G240" s="4"/>
       <c r="H240" s="4"/>
       <c r="I240" s="4"/>
     </row>
@@ -4226,7 +4080,6 @@
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
       <c r="F241" s="4"/>
-      <c r="G241" s="4"/>
       <c r="H241" s="4"/>
       <c r="I241" s="4"/>
     </row>
@@ -4237,7 +4090,6 @@
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
       <c r="F242" s="4"/>
-      <c r="G242" s="4"/>
       <c r="H242" s="4"/>
       <c r="I242" s="4"/>
     </row>
@@ -4248,7 +4100,6 @@
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
       <c r="F243" s="4"/>
-      <c r="G243" s="4"/>
       <c r="H243" s="4"/>
       <c r="I243" s="4"/>
     </row>
@@ -4259,7 +4110,6 @@
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
       <c r="F244" s="4"/>
-      <c r="G244" s="4"/>
       <c r="H244" s="4"/>
       <c r="I244" s="4"/>
     </row>
@@ -4270,7 +4120,6 @@
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
       <c r="F245" s="4"/>
-      <c r="G245" s="4"/>
       <c r="H245" s="4"/>
       <c r="I245" s="4"/>
     </row>
@@ -4281,7 +4130,6 @@
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
       <c r="F246" s="4"/>
-      <c r="G246" s="4"/>
       <c r="H246" s="4"/>
       <c r="I246" s="4"/>
     </row>
@@ -4292,7 +4140,6 @@
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
       <c r="F247" s="4"/>
-      <c r="G247" s="4"/>
       <c r="H247" s="4"/>
       <c r="I247" s="4"/>
     </row>
@@ -4303,7 +4150,6 @@
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
       <c r="F248" s="4"/>
-      <c r="G248" s="4"/>
       <c r="H248" s="4"/>
       <c r="I248" s="4"/>
     </row>
@@ -4314,7 +4160,6 @@
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
       <c r="F249" s="4"/>
-      <c r="G249" s="4"/>
       <c r="H249" s="4"/>
       <c r="I249" s="4"/>
     </row>
@@ -4325,7 +4170,6 @@
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
       <c r="F250" s="4"/>
-      <c r="G250" s="4"/>
       <c r="H250" s="4"/>
       <c r="I250" s="4"/>
     </row>
@@ -4336,7 +4180,6 @@
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
       <c r="F251" s="4"/>
-      <c r="G251" s="4"/>
       <c r="H251" s="4"/>
       <c r="I251" s="4"/>
     </row>
@@ -4347,7 +4190,6 @@
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
       <c r="F252" s="4"/>
-      <c r="G252" s="4"/>
       <c r="H252" s="4"/>
       <c r="I252" s="4"/>
     </row>
@@ -4358,7 +4200,6 @@
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
       <c r="F253" s="4"/>
-      <c r="G253" s="4"/>
       <c r="H253" s="4"/>
       <c r="I253" s="4"/>
     </row>
@@ -4369,7 +4210,6 @@
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
       <c r="F254" s="4"/>
-      <c r="G254" s="4"/>
       <c r="H254" s="4"/>
       <c r="I254" s="4"/>
     </row>
@@ -4380,7 +4220,6 @@
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
       <c r="F255" s="4"/>
-      <c r="G255" s="4"/>
       <c r="H255" s="4"/>
       <c r="I255" s="4"/>
     </row>
@@ -4391,7 +4230,6 @@
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
       <c r="F256" s="4"/>
-      <c r="G256" s="4"/>
       <c r="H256" s="4"/>
       <c r="I256" s="4"/>
     </row>
@@ -4402,7 +4240,6 @@
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
       <c r="F257" s="4"/>
-      <c r="G257" s="4"/>
       <c r="H257" s="4"/>
       <c r="I257" s="4"/>
     </row>
@@ -4413,7 +4250,6 @@
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
       <c r="F258" s="4"/>
-      <c r="G258" s="4"/>
       <c r="H258" s="4"/>
       <c r="I258" s="4"/>
     </row>
@@ -4424,7 +4260,6 @@
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
       <c r="F259" s="4"/>
-      <c r="G259" s="4"/>
       <c r="H259" s="4"/>
       <c r="I259" s="4"/>
     </row>
@@ -4435,7 +4270,6 @@
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
       <c r="F260" s="4"/>
-      <c r="G260" s="4"/>
       <c r="H260" s="4"/>
       <c r="I260" s="4"/>
     </row>
@@ -4446,7 +4280,6 @@
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
       <c r="F261" s="4"/>
-      <c r="G261" s="4"/>
       <c r="H261" s="4"/>
       <c r="I261" s="4"/>
     </row>
@@ -4457,7 +4290,6 @@
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
       <c r="F262" s="4"/>
-      <c r="G262" s="4"/>
       <c r="H262" s="4"/>
       <c r="I262" s="4"/>
     </row>
@@ -4468,7 +4300,6 @@
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
       <c r="F263" s="4"/>
-      <c r="G263" s="4"/>
       <c r="H263" s="4"/>
       <c r="I263" s="4"/>
     </row>
@@ -4479,7 +4310,6 @@
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
       <c r="F264" s="4"/>
-      <c r="G264" s="4"/>
       <c r="H264" s="4"/>
       <c r="I264" s="4"/>
     </row>
@@ -4490,7 +4320,6 @@
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
       <c r="F265" s="4"/>
-      <c r="G265" s="4"/>
       <c r="H265" s="4"/>
       <c r="I265" s="4"/>
     </row>
@@ -4501,7 +4330,6 @@
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
       <c r="F266" s="4"/>
-      <c r="G266" s="4"/>
       <c r="H266" s="4"/>
       <c r="I266" s="4"/>
     </row>
@@ -4512,7 +4340,6 @@
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
       <c r="F267" s="4"/>
-      <c r="G267" s="4"/>
       <c r="H267" s="4"/>
       <c r="I267" s="4"/>
     </row>
@@ -4523,7 +4350,6 @@
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
       <c r="F268" s="4"/>
-      <c r="G268" s="4"/>
       <c r="H268" s="4"/>
       <c r="I268" s="4"/>
     </row>
@@ -4534,7 +4360,6 @@
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
       <c r="F269" s="4"/>
-      <c r="G269" s="4"/>
       <c r="H269" s="4"/>
       <c r="I269" s="4"/>
     </row>
@@ -4545,7 +4370,6 @@
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
       <c r="F270" s="4"/>
-      <c r="G270" s="4"/>
       <c r="H270" s="4"/>
       <c r="I270" s="4"/>
     </row>
@@ -4556,7 +4380,6 @@
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
       <c r="F271" s="4"/>
-      <c r="G271" s="4"/>
       <c r="H271" s="4"/>
       <c r="I271" s="4"/>
     </row>
@@ -4567,7 +4390,6 @@
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
       <c r="F272" s="4"/>
-      <c r="G272" s="4"/>
       <c r="H272" s="4"/>
       <c r="I272" s="4"/>
     </row>
@@ -4578,7 +4400,6 @@
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
       <c r="F273" s="4"/>
-      <c r="G273" s="4"/>
       <c r="H273" s="4"/>
       <c r="I273" s="4"/>
     </row>
@@ -4589,7 +4410,6 @@
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
       <c r="F274" s="4"/>
-      <c r="G274" s="4"/>
       <c r="H274" s="4"/>
       <c r="I274" s="4"/>
     </row>
@@ -4600,7 +4420,6 @@
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
       <c r="F275" s="4"/>
-      <c r="G275" s="4"/>
       <c r="H275" s="4"/>
       <c r="I275" s="4"/>
     </row>
@@ -4611,7 +4430,6 @@
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
       <c r="F276" s="4"/>
-      <c r="G276" s="4"/>
       <c r="H276" s="4"/>
       <c r="I276" s="4"/>
     </row>
@@ -4622,7 +4440,6 @@
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
       <c r="F277" s="4"/>
-      <c r="G277" s="4"/>
       <c r="H277" s="4"/>
       <c r="I277" s="4"/>
     </row>
@@ -4633,7 +4450,6 @@
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
       <c r="F278" s="4"/>
-      <c r="G278" s="4"/>
       <c r="H278" s="4"/>
       <c r="I278" s="4"/>
     </row>
@@ -4644,7 +4460,6 @@
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
       <c r="F279" s="4"/>
-      <c r="G279" s="4"/>
       <c r="H279" s="4"/>
       <c r="I279" s="4"/>
     </row>
@@ -4655,7 +4470,6 @@
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
       <c r="F280" s="4"/>
-      <c r="G280" s="4"/>
       <c r="H280" s="4"/>
       <c r="I280" s="4"/>
     </row>
@@ -4666,7 +4480,6 @@
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
       <c r="F281" s="4"/>
-      <c r="G281" s="4"/>
       <c r="H281" s="4"/>
       <c r="I281" s="4"/>
     </row>
@@ -4677,7 +4490,6 @@
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
       <c r="F282" s="4"/>
-      <c r="G282" s="4"/>
       <c r="H282" s="4"/>
       <c r="I282" s="4"/>
     </row>
@@ -4688,7 +4500,6 @@
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
       <c r="F283" s="4"/>
-      <c r="G283" s="4"/>
       <c r="H283" s="4"/>
       <c r="I283" s="4"/>
     </row>
@@ -4699,7 +4510,6 @@
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
       <c r="F284" s="4"/>
-      <c r="G284" s="4"/>
       <c r="H284" s="4"/>
       <c r="I284" s="4"/>
     </row>
@@ -4710,7 +4520,6 @@
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
       <c r="F285" s="4"/>
-      <c r="G285" s="4"/>
       <c r="H285" s="4"/>
       <c r="I285" s="4"/>
     </row>
